--- a/1. ELICITACION/1.5 Backlog/GN°4_Backlog_PlantillaV2.xlsx
+++ b/1. ELICITACION/1.5 Backlog/GN°4_Backlog_PlantillaV2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoshPC\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoshPC\Documents\Universidad\Analisis y Diseño\Github\YulianaValencia_30724_G4_ADSW\1. ELICITACION\1.5 Backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CAB13A-6379-4507-86FB-06BC621DACF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C256FDC7-35A5-45CC-ACE3-FA3FCDE2024E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="219">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -560,6 +560,129 @@
   </si>
   <si>
     <t>Almacenar la información del técnico en la base de datos.</t>
+  </si>
+  <si>
+    <t>Sprint 2</t>
+  </si>
+  <si>
+    <t>REQ007</t>
+  </si>
+  <si>
+    <t>Edición de Mantenimientos</t>
+  </si>
+  <si>
+    <t>Restringir qué edita el Técnico.</t>
+  </si>
+  <si>
+    <t>REQ007-1</t>
+  </si>
+  <si>
+    <t>Diseñar vista de edición de orden (estado, costos, diagnóstico).</t>
+  </si>
+  <si>
+    <t>REQ007-2</t>
+  </si>
+  <si>
+    <t>Implementar actualización financiera (abonos y saldos) en BD.</t>
+  </si>
+  <si>
+    <t>REQ007-3</t>
+  </si>
+  <si>
+    <t>Configurar Proxy para bloquear modificación de costos a Técnicos.</t>
+  </si>
+  <si>
+    <t>REQ009</t>
+  </si>
+  <si>
+    <t>reasignar un técnico diferente a un mantenimiento</t>
+  </si>
+  <si>
+    <t>Mantener historial.</t>
+  </si>
+  <si>
+    <t>REQ009-1</t>
+  </si>
+  <si>
+    <t>Diseñar componente para cambiar de técnico en órdenes activas.</t>
+  </si>
+  <si>
+    <t>REQ009-2</t>
+  </si>
+  <si>
+    <t>Implementar la actualización de la relación técnico-orden en la BD.</t>
+  </si>
+  <si>
+    <t>REQ009-3</t>
+  </si>
+  <si>
+    <t>Registrar un log de auditoría del cambio de responsable.</t>
+  </si>
+  <si>
+    <t>REQ014</t>
+  </si>
+  <si>
+    <t>Edición y Baja de Técnicos</t>
+  </si>
+  <si>
+    <t>editar o eliminar la información de un técnico</t>
+  </si>
+  <si>
+    <t>mantener los perfiles al día o dar de baja a personal inactivo.</t>
+  </si>
+  <si>
+    <t>Baja lógica.</t>
+  </si>
+  <si>
+    <t>REQ014-1</t>
+  </si>
+  <si>
+    <t>Diseñar panel de edición de perfil y botón de desactivación.</t>
+  </si>
+  <si>
+    <t>REQ014-2</t>
+  </si>
+  <si>
+    <t>Implementar actualización de datos (especialidad, teléfono).</t>
+  </si>
+  <si>
+    <t>REQ014-3</t>
+  </si>
+  <si>
+    <t>Implementar baja lógica (estado inactivo) y ocultar en listas.</t>
+  </si>
+  <si>
+    <t>REQ016</t>
+  </si>
+  <si>
+    <t>Edición y Baja de Clientes</t>
+  </si>
+  <si>
+    <t>editar o eliminar perfiles de clientes</t>
+  </si>
+  <si>
+    <t>autogestionar datos o limpiar la base de datos del taller.</t>
+  </si>
+  <si>
+    <t>Evitar borrar historial.</t>
+  </si>
+  <si>
+    <t>REQ016-1</t>
+  </si>
+  <si>
+    <t>Diseñar interfaz de autogestión de perfil para el cliente.</t>
+  </si>
+  <si>
+    <t>REQ016-2</t>
+  </si>
+  <si>
+    <t>Implementar la actualización de datos de contacto en BD.</t>
+  </si>
+  <si>
+    <t>REQ016-3</t>
+  </si>
+  <si>
+    <t>Añadir función de eliminación lógica desde el panel del Administrador.</t>
   </si>
 </sst>
 </file>
@@ -703,7 +826,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -750,9 +873,12 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2494,7 +2620,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="12.44140625" customWidth="1"/>
-    <col min="3" max="3" width="21.44140625" customWidth="1"/>
+    <col min="3" max="3" width="29.6640625" customWidth="1"/>
     <col min="4" max="4" width="18.88671875" customWidth="1"/>
     <col min="5" max="5" width="29.21875" customWidth="1"/>
     <col min="6" max="6" width="56.109375" customWidth="1"/>
@@ -2630,7 +2756,7 @@
       <c r="B7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="20" t="s">
         <v>166</v>
       </c>
       <c r="D7" s="21"/>
@@ -2667,7 +2793,7 @@
       <c r="B8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="20" t="s">
         <v>167</v>
       </c>
       <c r="D8" s="21"/>
@@ -2704,7 +2830,7 @@
       <c r="B9" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="22" t="s">
         <v>168</v>
       </c>
       <c r="D9" s="21"/>
@@ -2781,7 +2907,7 @@
       <c r="B12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="20" t="s">
         <v>170</v>
       </c>
       <c r="D12" s="21"/>
@@ -2800,7 +2926,7 @@
       <c r="B13" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="20" t="s">
         <v>171</v>
       </c>
       <c r="D13" s="21"/>
@@ -2819,7 +2945,7 @@
       <c r="B14" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="22" t="s">
         <v>172</v>
       </c>
       <c r="D14" s="21"/>
@@ -2877,7 +3003,7 @@
       <c r="B17" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="20" t="s">
         <v>173</v>
       </c>
       <c r="D17" s="21"/>
@@ -2896,7 +3022,7 @@
       <c r="B18" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="20" t="s">
         <v>174</v>
       </c>
       <c r="D18" s="21"/>
@@ -2915,7 +3041,7 @@
       <c r="B19" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="22" t="s">
         <v>31</v>
       </c>
       <c r="D19" s="21"/>
@@ -2973,7 +3099,7 @@
       <c r="B22" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="20" t="s">
         <v>175</v>
       </c>
       <c r="D22" s="21"/>
@@ -2992,7 +3118,7 @@
       <c r="B23" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="20" t="s">
         <v>176</v>
       </c>
       <c r="D23" s="21"/>
@@ -3011,7 +3137,7 @@
       <c r="B24" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="22" t="s">
         <v>177</v>
       </c>
       <c r="D24" s="21"/>
@@ -3079,7 +3205,7 @@
       <c r="B31" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="22" t="s">
+      <c r="C31" s="20" t="s">
         <v>146</v>
       </c>
       <c r="D31" s="21"/>
@@ -3098,7 +3224,7 @@
       <c r="B32" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="20" t="s">
         <v>147</v>
       </c>
       <c r="D32" s="21"/>
@@ -3117,7 +3243,7 @@
       <c r="B33" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="20" t="s">
+      <c r="C33" s="22" t="s">
         <v>148</v>
       </c>
       <c r="D33" s="21"/>
@@ -3177,7 +3303,7 @@
       <c r="B36" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="22" t="s">
+      <c r="C36" s="20" t="s">
         <v>151</v>
       </c>
       <c r="D36" s="21"/>
@@ -3196,7 +3322,7 @@
       <c r="B37" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="22" t="s">
+      <c r="C37" s="20" t="s">
         <v>152</v>
       </c>
       <c r="D37" s="21"/>
@@ -3215,7 +3341,7 @@
       <c r="B38" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C38" s="20" t="s">
+      <c r="C38" s="22" t="s">
         <v>153</v>
       </c>
       <c r="D38" s="21"/>
@@ -3273,7 +3399,7 @@
       <c r="B41" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C41" s="22" t="s">
+      <c r="C41" s="20" t="s">
         <v>155</v>
       </c>
       <c r="D41" s="21"/>
@@ -3292,7 +3418,7 @@
       <c r="B42" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C42" s="22" t="s">
+      <c r="C42" s="20" t="s">
         <v>156</v>
       </c>
       <c r="D42" s="21"/>
@@ -3311,7 +3437,7 @@
       <c r="B43" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="20" t="s">
+      <c r="C43" s="22" t="s">
         <v>157</v>
       </c>
       <c r="D43" s="21"/>
@@ -3369,7 +3495,7 @@
       <c r="B46" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="C46" s="22" t="s">
+      <c r="C46" s="20" t="s">
         <v>160</v>
       </c>
       <c r="D46" s="21"/>
@@ -3388,7 +3514,7 @@
       <c r="B47" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="C47" s="22" t="s">
+      <c r="C47" s="20" t="s">
         <v>162</v>
       </c>
       <c r="D47" s="21"/>
@@ -3407,7 +3533,7 @@
       <c r="B48" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="C48" s="20" t="s">
+      <c r="C48" s="22" t="s">
         <v>164</v>
       </c>
       <c r="D48" s="21"/>
@@ -3422,38 +3548,414 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="49" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="50" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="51" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B51" s="19" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="53" spans="2:10" ht="26.4" customHeight="1">
+      <c r="B53" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="I53" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J53" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" ht="15.75" customHeight="1">
+      <c r="C54" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B55" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="C55" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="21"/>
+      <c r="G55" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="H55" s="11"/>
+      <c r="I55" s="11"/>
+      <c r="J55" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B56" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="21"/>
+      <c r="G56" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="H56" s="11"/>
+      <c r="I56" s="11"/>
+      <c r="J56" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B57" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C57" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="21"/>
+      <c r="G57" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" ht="28.8" customHeight="1">
+      <c r="B58" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J58" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" ht="15.75" customHeight="1">
+      <c r="C59" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I59" s="8"/>
+      <c r="J59" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B60" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="C60" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="21"/>
+      <c r="G60" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="H60" s="11"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B61" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="C61" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="21"/>
+      <c r="G61" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11"/>
+      <c r="J61" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B62" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C62" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="D62" s="21"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="21"/>
+      <c r="G62" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" ht="26.4" customHeight="1">
+      <c r="B63" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D63" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="I63" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J63" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" ht="15.75" customHeight="1">
+      <c r="C64" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I64" s="8"/>
+      <c r="J64" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B65" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="C65" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="21"/>
+      <c r="G65" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="H65" s="11"/>
+      <c r="I65" s="11"/>
+      <c r="J65" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B66" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="C66" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="21"/>
+      <c r="G66" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="H66" s="11"/>
+      <c r="I66" s="11"/>
+      <c r="J66" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B67" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="C67" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="21"/>
+      <c r="G67" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="H67" s="14"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" ht="25.8" customHeight="1">
+      <c r="B68" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="D68" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="H68" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="I68" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J68" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" ht="15.75" customHeight="1">
+      <c r="C69" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I69" s="8"/>
+      <c r="J69" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B70" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C70" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="H70" s="11"/>
+      <c r="I70" s="11"/>
+      <c r="J70" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B71" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C71" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="H71" s="11"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B72" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="C72" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="74" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="75" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="76" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="77" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="78" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="79" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="80" spans="2:10" ht="15.75" customHeight="1"/>
     <row r="81" ht="15.75" customHeight="1"/>
     <row r="82" ht="15.75" customHeight="1"/>
     <row r="83" ht="15.75" customHeight="1"/>
@@ -4309,15 +4811,19 @@
     <row r="933" ht="15.75" customHeight="1"/>
     <row r="934" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="C41:F41"/>
-    <mergeCell ref="C42:F42"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C33:F33"/>
+  <mergeCells count="36">
+    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="C72:F72"/>
+    <mergeCell ref="C55:F55"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="C65:F65"/>
+    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="C66:F66"/>
+    <mergeCell ref="C67:F67"/>
+    <mergeCell ref="C56:F56"/>
+    <mergeCell ref="C57:F57"/>
     <mergeCell ref="C43:F43"/>
     <mergeCell ref="C46:F46"/>
     <mergeCell ref="C47:F47"/>
@@ -4334,6 +4840,14 @@
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="C42:F42"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C33:F33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/1. ELICITACION/1.5 Backlog/GN°4_Backlog_PlantillaV2.xlsx
+++ b/1. ELICITACION/1.5 Backlog/GN°4_Backlog_PlantillaV2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoshPC\Documents\Universidad\Analisis y Diseño\Github\YulianaValencia_30724_G4_ADSW\1. ELICITACION\1.5 Backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C256FDC7-35A5-45CC-ACE3-FA3FCDE2024E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4165BAD-FB0A-44BE-A688-1C7C6BCEA06A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,19 @@
     <sheet name="Backlog" sheetId="1" r:id="rId1"/>
     <sheet name="Sprint0, Sprint 1 y Sprint 2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="gOOwe9YsOCoiWqIBIF9JDcJ+1RIaKRd9hc06srVPJSM="/>
     </ext>
@@ -26,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="286">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -683,13 +694,350 @@
   </si>
   <si>
     <t>Añadir función de eliminación lógica desde el panel del Administrador.</t>
+  </si>
+  <si>
+    <t>Notificaciones Externas</t>
+  </si>
+  <si>
+    <t>seleccionar un mantenimiento y elegir "Enviar por WhatsApp" o Correo</t>
+  </si>
+  <si>
+    <t>notificar de forma automatizada al cliente enviando el documento del reporte.</t>
+  </si>
+  <si>
+    <t>Validar timeouts de red.</t>
+  </si>
+  <si>
+    <t>RF11-1</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Maquetar en </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>UI_ModuloGestion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> los botones de selección de canal y alertas de estado.</t>
+    </r>
+  </si>
+  <si>
+    <t>RF11-2</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implementar la función </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>generarDocumentoPDF(idMant)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> con los datos de la orden.</t>
+    </r>
+  </si>
+  <si>
+    <t>RF11-3</t>
+  </si>
+  <si>
+    <t>Implementar interfaz del patrón Bridge para estandarizar proveedores de mensajería.</t>
+  </si>
+  <si>
+    <t>RF11-4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Desarrollar </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>enviarWhatsApp(numero: String, documento: File)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>API_Notificaciones</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>RF11-5</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Desarrollar </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>enviarCorreo(email: String, documento: File)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> en </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>API_Notificaciones</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>RF11-6</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Configurar en el controlador la captura de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>confirmacionEnvio(true)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> para actualizar la pantalla.</t>
+    </r>
+  </si>
+  <si>
+    <t>Sprint 3</t>
+  </si>
+  <si>
+    <t>Consultar Clientes</t>
+  </si>
+  <si>
+    <t>consultar clientes registrados en el sistema</t>
+  </si>
+  <si>
+    <t>visualizar a los usuarios mediante búsquedas y ordenaciones.</t>
+  </si>
+  <si>
+    <t>RF15-1</t>
+  </si>
+  <si>
+    <t>Diseñar panel de listado de clientes y herramientas de ordenación.</t>
+  </si>
+  <si>
+    <t>RF15-2</t>
+  </si>
+  <si>
+    <t>Construir la lógica de ordenación alfabética y búsquedas en BD.</t>
+  </si>
+  <si>
+    <t>RF15-3</t>
+  </si>
+  <si>
+    <t>Validar el funcionamiento de los filtros y visualización de la cartera.</t>
+  </si>
+  <si>
+    <t>Consultar Mantenimientos de Perfil</t>
+  </si>
+  <si>
+    <t>consultar todos los mantenimientos del perfil</t>
+  </si>
+  <si>
+    <t>monitorear órdenes propias con búsquedas, filtros y ordenaciones.</t>
+  </si>
+  <si>
+    <t>Restringir vista a datos propios.</t>
+  </si>
+  <si>
+    <t>RF17-1</t>
+  </si>
+  <si>
+    <t>Diseñar vista de mantenimientos exclusiva para el panel del cliente.</t>
+  </si>
+  <si>
+    <t>RF17-2</t>
+  </si>
+  <si>
+    <t>Desplegar lista de mantenimientos filtrando por el ID de sesión actual.</t>
+  </si>
+  <si>
+    <t>RF17-3</t>
+  </si>
+  <si>
+    <t>Validar que el cliente solo pueda buscar por ID de sus propias órdenes.</t>
+  </si>
+  <si>
+    <t>Sprint 4</t>
+  </si>
+  <si>
+    <t>Imprimir Informe</t>
+  </si>
+  <si>
+    <t>Permitir imprimir la información solicitada.</t>
+  </si>
+  <si>
+    <t>Obtener un informe físico o digital previo a la ejecución.</t>
+  </si>
+  <si>
+    <t>Generación de formato PDF.</t>
+  </si>
+  <si>
+    <t>RF10-1</t>
+  </si>
+  <si>
+    <t>Diseñar componentes en Angular para la interfaz de impresión y botones de descarga.</t>
+  </si>
+  <si>
+    <t>RF10-2</t>
+  </si>
+  <si>
+    <t>Integrar librería de generación de reportes PDF implementando el patrón Adapter en el backend.</t>
+  </si>
+  <si>
+    <t>RF10-3</t>
+  </si>
+  <si>
+    <t>Validar el despliegue correcto del documento con los datos extraídos de la orden.</t>
+  </si>
+  <si>
+    <t>Olvidar contraseña</t>
+  </si>
+  <si>
+    <t>Deberá permitir la recuperación de la contraseña.</t>
+  </si>
+  <si>
+    <t>Recuperar el acceso al perfil de forma autónoma.</t>
+  </si>
+  <si>
+    <t>Integración con servidor de correo.</t>
+  </si>
+  <si>
+    <t>RF02-1</t>
+  </si>
+  <si>
+    <t>Diseñar formulario de "Olvidé mi contraseña" para capturar el correo del usuario.</t>
+  </si>
+  <si>
+    <t>RF02-2</t>
+  </si>
+  <si>
+    <t>Implementar módulo de envío de correo en Node.js con enlace temporal de reseteo.</t>
+  </si>
+  <si>
+    <t>RF02-3</t>
+  </si>
+  <si>
+    <t>Consultar Mantenimientos Asignados</t>
+  </si>
+  <si>
+    <t>Consultar todos los mantenimientos asignados.</t>
+  </si>
+  <si>
+    <t>Visualizar las reparaciones pendientes con búsquedas y filtros.</t>
+  </si>
+  <si>
+    <t>Filtrar mantenimientos activos donde el técnico asignado sea el usuario en sesión.</t>
+  </si>
+  <si>
+    <t>RF18-1</t>
+  </si>
+  <si>
+    <t>Diseñar vista del panel del técnico con lista interactiva de mantenimientos.</t>
+  </si>
+  <si>
+    <t>RF18-2</t>
+  </si>
+  <si>
+    <t>Implementar filtros dinámicos en la base de datos vinculados estrictamente al ID de la sesión.</t>
+  </si>
+  <si>
+    <t>RF18-3</t>
+  </si>
+  <si>
+    <t>Validar que el inicio de sesión del técnico despliegue exclusivamente su jornada laboral.</t>
+  </si>
+  <si>
+    <t>Añadir validaciones de seguridad (ej. fuerza de contraseña) al momento de actualizar.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -771,6 +1119,18 @@
       <color rgb="FF073763"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -873,14 +1233,14 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2616,7 +2976,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA934"/>
+  <dimension ref="A1:AA930"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="12.44140625" customWidth="1"/>
@@ -2756,12 +3116,12 @@
       <c r="B7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
       <c r="G7" s="11" t="s">
         <v>154</v>
       </c>
@@ -2793,12 +3153,12 @@
       <c r="B8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
       <c r="G8" s="13" t="s">
         <v>154</v>
       </c>
@@ -2830,12 +3190,12 @@
       <c r="B9" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
       <c r="G9" s="13" t="s">
         <v>154</v>
       </c>
@@ -2907,12 +3267,12 @@
       <c r="B12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
       <c r="G12" s="11" t="s">
         <v>149</v>
       </c>
@@ -2926,12 +3286,12 @@
       <c r="B13" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
       <c r="G13" s="13" t="s">
         <v>149</v>
       </c>
@@ -2945,12 +3305,12 @@
       <c r="B14" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
       <c r="G14" s="13" t="s">
         <v>149</v>
       </c>
@@ -3003,12 +3363,12 @@
       <c r="B17" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
       <c r="G17" s="11" t="s">
         <v>144</v>
       </c>
@@ -3022,12 +3382,12 @@
       <c r="B18" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
       <c r="G18" s="13" t="s">
         <v>144</v>
       </c>
@@ -3041,12 +3401,12 @@
       <c r="B19" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
       <c r="G19" s="13" t="s">
         <v>144</v>
       </c>
@@ -3099,12 +3459,12 @@
       <c r="B22" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
       <c r="G22" s="11" t="s">
         <v>154</v>
       </c>
@@ -3118,12 +3478,12 @@
       <c r="B23" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
       <c r="G23" s="13" t="s">
         <v>154</v>
       </c>
@@ -3137,12 +3497,12 @@
       <c r="B24" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
       <c r="G24" s="13" t="s">
         <v>154</v>
       </c>
@@ -3205,12 +3565,12 @@
       <c r="B31" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
       <c r="G31" s="11" t="s">
         <v>144</v>
       </c>
@@ -3224,12 +3584,12 @@
       <c r="B32" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
       <c r="G32" s="13" t="s">
         <v>144</v>
       </c>
@@ -3243,12 +3603,12 @@
       <c r="B33" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
       <c r="G33" s="13" t="s">
         <v>144</v>
       </c>
@@ -3303,12 +3663,12 @@
       <c r="B36" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="20" t="s">
+      <c r="C36" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
       <c r="G36" s="11" t="s">
         <v>149</v>
       </c>
@@ -3322,12 +3682,12 @@
       <c r="B37" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="20" t="s">
+      <c r="C37" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
       <c r="G37" s="13" t="s">
         <v>149</v>
       </c>
@@ -3341,12 +3701,12 @@
       <c r="B38" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C38" s="22" t="s">
+      <c r="C38" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
       <c r="G38" s="13" t="s">
         <v>149</v>
       </c>
@@ -3399,12 +3759,12 @@
       <c r="B41" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
       <c r="G41" s="11" t="s">
         <v>154</v>
       </c>
@@ -3418,12 +3778,12 @@
       <c r="B42" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C42" s="20" t="s">
+      <c r="C42" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
       <c r="G42" s="13" t="s">
         <v>154</v>
       </c>
@@ -3437,12 +3797,12 @@
       <c r="B43" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="22" t="s">
+      <c r="C43" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
       <c r="G43" s="13" t="s">
         <v>154</v>
       </c>
@@ -3495,12 +3855,12 @@
       <c r="B46" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="C46" s="20" t="s">
+      <c r="C46" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="21"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="22"/>
       <c r="G46" s="11" t="s">
         <v>144</v>
       </c>
@@ -3514,12 +3874,12 @@
       <c r="B47" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="C47" s="20" t="s">
+      <c r="C47" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
       <c r="G47" s="13" t="s">
         <v>144</v>
       </c>
@@ -3533,12 +3893,12 @@
       <c r="B48" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="C48" s="22" t="s">
+      <c r="C48" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="22"/>
       <c r="G48" s="13" t="s">
         <v>144</v>
       </c>
@@ -3601,12 +3961,12 @@
       <c r="B55" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="C55" s="20" t="s">
+      <c r="C55" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
       <c r="G55" s="11" t="s">
         <v>149</v>
       </c>
@@ -3620,12 +3980,12 @@
       <c r="B56" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="C56" s="20" t="s">
+      <c r="C56" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="D56" s="21"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="21"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
       <c r="G56" s="11" t="s">
         <v>149</v>
       </c>
@@ -3639,12 +3999,12 @@
       <c r="B57" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="C57" s="22" t="s">
+      <c r="C57" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="D57" s="21"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="21"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
       <c r="G57" s="11" t="s">
         <v>149</v>
       </c>
@@ -3664,7 +4024,7 @@
       <c r="D58" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E58" s="23" t="s">
+      <c r="E58" s="20" t="s">
         <v>189</v>
       </c>
       <c r="F58" s="10" t="s">
@@ -3699,12 +4059,12 @@
       <c r="B60" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="C60" s="20" t="s">
+      <c r="C60" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="D60" s="21"/>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="22"/>
       <c r="G60" s="13" t="s">
         <v>154</v>
       </c>
@@ -3718,12 +4078,12 @@
       <c r="B61" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="C61" s="20" t="s">
+      <c r="C61" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="D61" s="21"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="21"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
       <c r="G61" s="13" t="s">
         <v>154</v>
       </c>
@@ -3737,12 +4097,12 @@
       <c r="B62" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="C62" s="22" t="s">
+      <c r="C62" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="D62" s="21"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="21"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
       <c r="G62" s="13" t="s">
         <v>154</v>
       </c>
@@ -3759,7 +4119,7 @@
       <c r="C63" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="D63" s="23" t="s">
+      <c r="D63" s="20" t="s">
         <v>9</v>
       </c>
       <c r="E63" s="10" t="s">
@@ -3797,12 +4157,12 @@
       <c r="B65" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="C65" s="20" t="s">
+      <c r="C65" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
       <c r="G65" s="13" t="s">
         <v>144</v>
       </c>
@@ -3816,12 +4176,12 @@
       <c r="B66" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="C66" s="20" t="s">
+      <c r="C66" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="22"/>
       <c r="G66" s="13" t="s">
         <v>144</v>
       </c>
@@ -3835,12 +4195,12 @@
       <c r="B67" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="C67" s="22" t="s">
+      <c r="C67" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="D67" s="21"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="21"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
       <c r="G67" s="13" t="s">
         <v>144</v>
       </c>
@@ -3851,13 +4211,13 @@
       </c>
     </row>
     <row r="68" spans="2:10" ht="25.8" customHeight="1">
-      <c r="B68" s="23" t="s">
+      <c r="B68" s="20" t="s">
         <v>208</v>
       </c>
       <c r="C68" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="D68" s="23" t="s">
+      <c r="D68" s="20" t="s">
         <v>9</v>
       </c>
       <c r="E68" s="10" t="s">
@@ -3895,12 +4255,12 @@
       <c r="B70" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="C70" s="20" t="s">
+      <c r="C70" s="21" t="s">
         <v>214</v>
       </c>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
       <c r="G70" s="13" t="s">
         <v>154</v>
       </c>
@@ -3914,12 +4274,12 @@
       <c r="B71" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="C71" s="20" t="s">
+      <c r="C71" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
       <c r="G71" s="13" t="s">
         <v>154</v>
       </c>
@@ -3933,12 +4293,12 @@
       <c r="B72" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="C72" s="22" t="s">
+      <c r="C72" s="23" t="s">
         <v>218</v>
       </c>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="21"/>
+      <c r="D72" s="22"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="22"/>
       <c r="G72" s="13" t="s">
         <v>154</v>
       </c>
@@ -3950,60 +4310,708 @@
     </row>
     <row r="73" spans="2:10" ht="15.75" customHeight="1"/>
     <row r="74" spans="2:10" ht="15.75" customHeight="1"/>
-    <row r="75" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="75" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B75" s="19" t="s">
+        <v>235</v>
+      </c>
+    </row>
     <row r="76" spans="2:10" ht="15.75" customHeight="1"/>
-    <row r="77" spans="2:10" ht="15.75" customHeight="1"/>
-    <row r="78" spans="2:10" ht="15.75" customHeight="1"/>
-    <row r="79" spans="2:10" ht="15.75" customHeight="1"/>
-    <row r="80" spans="2:10" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="77" spans="2:10" ht="24" customHeight="1">
+      <c r="B77" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="I77" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J77" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B78" s="11"/>
+      <c r="C78" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="F78" s="22"/>
+      <c r="G78" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H78" s="11"/>
+      <c r="I78" s="11"/>
+      <c r="J78" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B79" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C79" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="H79" s="11"/>
+      <c r="I79" s="11"/>
+      <c r="J79" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B80" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="F80" s="22"/>
+      <c r="G80" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="H80" s="11"/>
+      <c r="I80" s="11"/>
+      <c r="J80" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B81" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="D81" s="22"/>
+      <c r="E81" s="22"/>
+      <c r="F81" s="22"/>
+      <c r="G81" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="H81" s="11"/>
+      <c r="I81" s="11"/>
+      <c r="J81" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B82" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C82" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="F82" s="22"/>
+      <c r="G82" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="H82" s="11"/>
+      <c r="I82" s="11"/>
+      <c r="J82" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B83" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="C83" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="F83" s="22"/>
+      <c r="G83" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="H83" s="11"/>
+      <c r="I83" s="11"/>
+      <c r="J83" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B84" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="C84" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="D84" s="22"/>
+      <c r="E84" s="22"/>
+      <c r="F84" s="22"/>
+      <c r="G84" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="H84" s="11"/>
+      <c r="I84" s="11"/>
+      <c r="J84" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B85" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D85" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="H85" s="10"/>
+      <c r="I85" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J85" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B86" s="11"/>
+      <c r="C86" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="F86" s="22"/>
+      <c r="G86" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H86" s="11"/>
+      <c r="I86" s="11"/>
+      <c r="J86" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B87" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="C87" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="F87" s="22"/>
+      <c r="G87" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="H87" s="11"/>
+      <c r="I87" s="11"/>
+      <c r="J87" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B88" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="C88" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="F88" s="22"/>
+      <c r="G88" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="H88" s="11"/>
+      <c r="I88" s="11"/>
+      <c r="J88" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B89" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C89" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="D89" s="22"/>
+      <c r="E89" s="22"/>
+      <c r="F89" s="22"/>
+      <c r="G89" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="H89" s="11"/>
+      <c r="I89" s="11"/>
+      <c r="J89" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B90" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="D90" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="G90" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="H90" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="I90" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J90" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B91" s="11"/>
+      <c r="C91" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D91" s="22"/>
+      <c r="E91" s="22"/>
+      <c r="F91" s="22"/>
+      <c r="G91" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H91" s="11"/>
+      <c r="I91" s="11"/>
+      <c r="J91" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B92" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="C92" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="D92" s="22"/>
+      <c r="E92" s="22"/>
+      <c r="F92" s="22"/>
+      <c r="G92" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="H92" s="11"/>
+      <c r="I92" s="11"/>
+      <c r="J92" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B93" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C93" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="D93" s="22"/>
+      <c r="E93" s="22"/>
+      <c r="F93" s="22"/>
+      <c r="G93" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="H93" s="11"/>
+      <c r="I93" s="11"/>
+      <c r="J93" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B94" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="C94" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="D94" s="22"/>
+      <c r="E94" s="22"/>
+      <c r="F94" s="22"/>
+      <c r="G94" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="H94" s="11"/>
+      <c r="I94" s="11"/>
+      <c r="J94" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="96" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="97" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B97" s="19" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="99" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B99" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C99" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="D99" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="G99" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="I99" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J99" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B100" s="11"/>
+      <c r="C100" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D100" s="22"/>
+      <c r="E100" s="22"/>
+      <c r="F100" s="22"/>
+      <c r="G100" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H100" s="11"/>
+      <c r="I100" s="11"/>
+      <c r="J100" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B101" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C101" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="D101" s="22"/>
+      <c r="E101" s="22"/>
+      <c r="F101" s="22"/>
+      <c r="G101" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="H101" s="11"/>
+      <c r="I101" s="11"/>
+      <c r="J101" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B102" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="C102" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="D102" s="22"/>
+      <c r="E102" s="22"/>
+      <c r="F102" s="22"/>
+      <c r="G102" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="H102" s="11"/>
+      <c r="I102" s="11"/>
+      <c r="J102" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B103" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="C103" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="D103" s="22"/>
+      <c r="E103" s="22"/>
+      <c r="F103" s="22"/>
+      <c r="G103" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="H103" s="11"/>
+      <c r="I103" s="11"/>
+      <c r="J103" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B104" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="D104" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="F104" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="G104" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="H104" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="I104" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J104" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="105" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B105" s="11"/>
+      <c r="C105" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D105" s="22"/>
+      <c r="E105" s="22"/>
+      <c r="F105" s="22"/>
+      <c r="G105" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H105" s="11"/>
+      <c r="I105" s="11"/>
+      <c r="J105" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="106" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B106" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="C106" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="D106" s="22"/>
+      <c r="E106" s="22"/>
+      <c r="F106" s="22"/>
+      <c r="G106" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="H106" s="11"/>
+      <c r="I106" s="11"/>
+      <c r="J106" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B107" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="C107" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="D107" s="22"/>
+      <c r="E107" s="22"/>
+      <c r="F107" s="22"/>
+      <c r="G107" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="H107" s="11"/>
+      <c r="I107" s="11"/>
+      <c r="J107" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B108" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="C108" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="D108" s="22"/>
+      <c r="E108" s="22"/>
+      <c r="F108" s="22"/>
+      <c r="G108" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="H108" s="11"/>
+      <c r="I108" s="11"/>
+      <c r="J108" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B109" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C109" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="D109" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="F109" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="G109" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="H109" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="I109" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J109" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="110" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B110" s="11"/>
+      <c r="C110" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D110" s="22"/>
+      <c r="E110" s="22"/>
+      <c r="F110" s="22"/>
+      <c r="G110" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H110" s="11"/>
+      <c r="I110" s="11"/>
+      <c r="J110" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="111" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B111" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="C111" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="D111" s="22"/>
+      <c r="E111" s="22"/>
+      <c r="F111" s="22"/>
+      <c r="G111" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="H111" s="11"/>
+      <c r="I111" s="11"/>
+      <c r="J111" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B112" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="C112" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="D112" s="22"/>
+      <c r="E112" s="22"/>
+      <c r="F112" s="22"/>
+      <c r="G112" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="H112" s="11"/>
+      <c r="I112" s="11"/>
+      <c r="J112" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="2:10" ht="15.75" customHeight="1">
+      <c r="B113" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="C113" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="D113" s="22"/>
+      <c r="E113" s="22"/>
+      <c r="F113" s="22"/>
+      <c r="G113" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="H113" s="11"/>
+      <c r="I113" s="11"/>
+      <c r="J113" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="115" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="116" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="117" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="118" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="119" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="120" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="121" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="122" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="123" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="124" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="125" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="126" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="127" spans="2:10" ht="15.75" customHeight="1"/>
+    <row r="128" spans="2:10" ht="15.75" customHeight="1"/>
     <row r="129" ht="15.75" customHeight="1"/>
     <row r="130" ht="15.75" customHeight="1"/>
     <row r="131" ht="15.75" customHeight="1"/>
@@ -4806,12 +5814,28 @@
     <row r="928" ht="15.75" customHeight="1"/>
     <row r="929" ht="15.75" customHeight="1"/>
     <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="63">
+    <mergeCell ref="C108:F108"/>
+    <mergeCell ref="C110:F110"/>
+    <mergeCell ref="C111:F111"/>
+    <mergeCell ref="C112:F112"/>
+    <mergeCell ref="C113:F113"/>
+    <mergeCell ref="C102:F102"/>
+    <mergeCell ref="C103:F103"/>
+    <mergeCell ref="C105:F105"/>
+    <mergeCell ref="C106:F106"/>
+    <mergeCell ref="C107:F107"/>
+    <mergeCell ref="C92:F92"/>
+    <mergeCell ref="C93:F93"/>
+    <mergeCell ref="C94:F94"/>
+    <mergeCell ref="C100:F100"/>
+    <mergeCell ref="C101:F101"/>
+    <mergeCell ref="C86:F86"/>
+    <mergeCell ref="C87:F87"/>
+    <mergeCell ref="C88:F88"/>
+    <mergeCell ref="C89:F89"/>
+    <mergeCell ref="C91:F91"/>
     <mergeCell ref="C71:F71"/>
     <mergeCell ref="C72:F72"/>
     <mergeCell ref="C55:F55"/>
@@ -4848,6 +5872,13 @@
     <mergeCell ref="C37:F37"/>
     <mergeCell ref="C38:F38"/>
     <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C83:F83"/>
+    <mergeCell ref="C84:F84"/>
+    <mergeCell ref="C81:F81"/>
+    <mergeCell ref="C82:F82"/>
+    <mergeCell ref="C78:F78"/>
+    <mergeCell ref="C79:F79"/>
+    <mergeCell ref="C80:F80"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
